--- a/output/2026-09-03_00_Italia_Campania_Cleaning.xlsx
+++ b/output/2026-09-03_00_Italia_Campania_Cleaning.xlsx
@@ -578,7 +578,6 @@
           <t>0824 1755622</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Confermato tramite elenchi telefonici/aziendali (elenchitelefonici.it, reteimprese.it, bluaziende.com) come attività nel settore macchine per la pulizia industriale, Zona Industriale Pezzapiano, Benevento.</t>
@@ -586,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -628,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -658,7 +657,6 @@
           <t>0825 675879</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Confermato: impresa attiva a Manocalzati (AV), P.IVA 01915560641, specializzata in impianti di aspirazione polveri, abbattimento fumi e depurazione aria (dust collector).</t>
@@ -666,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -708,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -750,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -780,7 +778,6 @@
           <t>081 932493</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Confermato: concessionario Unicarriers carrelli elevatori, vendita/assistenza macchine per pulizia Comac (lavapavimenti, spazzatrici), sede Via Nazionale 140, Nocera Superiore (SA).</t>
@@ -788,7 +785,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -798,7 +795,6 @@
           <t>O.M.B. S.r.l. (Officine Meccaniche Bartiromo)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Salerno</t>
@@ -826,7 +822,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -868,7 +864,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -910,7 +906,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -940,7 +936,6 @@
           <t>081 8186776</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Confermato: azienda con sedi a Qualiano (NA), Teverola (CE) e Capaccio Scalo (SA); dealer Doosan/Crown/Caterpillar/JLG per carrelli elevatori e piattaforme aeree, offre anche macchine per pulizia industriale e urbana a noleggio. Sede operativa in provincia di Salerno confermata.</t>
@@ -948,7 +943,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1037,6 @@
           <t>SA.VI Service S.r.l.</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Caserta</t>
@@ -1053,8 +1047,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Confermato tramite Europages: commercio, noleggio e rappresentanza di macchine per pulizia domestica/industriale, impianti di lavaggio, lavamoquette. Sede Via Nazionale Appia, Caserta. Attenzione: esiste entità omonima/collegata 'Sa.vi. Service Due S.r.l.s.' allo stesso indirizzo (P.IVA 04200290619) - da verificare quale sia l'entità operativa attuale prima di un contatto commerciale.</t>
@@ -1092,7 +1084,6 @@
           <t>0823 421062</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Confermato: azienda con 19 dipendenti e fatturato ~9,3 mln, leader in Campania per vendita/noleggio carrelli elevatori CAT/BYD, scaffalature e macchine per pulizia Nilfisk (lavasciuga, spazzatrici). Sede San Marco Evangelista (CE).</t>
@@ -1130,7 +1121,6 @@
           <t>081 19916857 / 320 0429494</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Confermato: azienda dedicata a vendita e noleggio di lavapavimenti, idropulitrici, monospazzola, carrelli pulizia, generatori vapore, lavamoquette e spazzatrici. Sede Via Sossio Russo 54, Frattamaggiore (NA).</t>

--- a/output/2026-09-03_00_Italia_Campania_Cleaning.xlsx
+++ b/output/2026-09-03_00_Italia_Campania_Cleaning.xlsx
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Confermato: azienda napoletana specializzata in impianti e sistemi di aspirazione (soffitti aspiranti, cappe industriali, abbattitori di fuliggine). Sede Via Luigi Volpicella 51, Napoli.</t>
+          <t>Confermato: azienda napoletana specializzata in impianti e sistemi di aspirazione (soffitti aspiranti, cappe industriali, abbattitori di fuliggine). Sede Via Luigi Volpicella 51, Napoli. [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
